--- a/Mau_nhap_khoa_dao_tao.xlsx
+++ b/Mau_nhap_khoa_dao_tao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5512528-AE1F-4E22-B1EA-7437652E3861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EE116A-E637-4A86-B4E5-017702270761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
   </bookViews>
   <sheets>
     <sheet name="KHOA_DAO_TAO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
   <si>
     <t>Mã tạm khóa (*)</t>
   </si>
@@ -51,12 +51,6 @@
     <t>Ngày kết thúc (*)</t>
   </si>
   <si>
-    <t>Giờ bắt đầu</t>
-  </si>
-  <si>
-    <t>Giờ kết thúc</t>
-  </si>
-  <si>
     <t>Địa điểm</t>
   </si>
   <si>
@@ -75,15 +69,6 @@
     <t>K001</t>
   </si>
   <si>
-    <t>Ví dụ: Kỹ năng phân tích dữ liệu</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
     <t>Hà Nội</t>
   </si>
   <si>
@@ -102,12 +87,6 @@
     <t>K002</t>
   </si>
   <si>
-    <t>Ví dụ: Quản trị rủi ro</t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
     <t>Trần Văn B</t>
   </si>
   <si>
@@ -268,13 +247,28 @@
   </si>
   <si>
     <t>Dương Thu Hương</t>
+  </si>
+  <si>
+    <t>Ngày học thực tế</t>
+  </si>
+  <si>
+    <t>Ví dụ: Khóa học liên tục</t>
+  </si>
+  <si>
+    <t>Ví dụ: Khóa học cách ngày</t>
+  </si>
+  <si>
+    <t>05/09/2026; 07/09/2026; 10/09/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,8 +307,26 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tiem"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Tiem"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,6 +348,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,16 +385,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -387,10 +400,24 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,129 +732,194 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF67E0AC-AADB-4307-AE13-44DC1057F665}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="10" width="24.86328125" customWidth="1"/>
     <col min="11" max="11" width="20.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="B2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="12">
+        <v>46151</v>
+      </c>
+      <c r="D2" s="12">
+        <v>46212</v>
+      </c>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="G2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="H2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="I2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="J2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="G2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="B3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="12">
+        <v>46151</v>
+      </c>
+      <c r="D3" s="12">
+        <v>46304</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -840,84 +932,84 @@
     <col min="7" max="7" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="28.5">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="28.5">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>31</v>
+      <c r="B1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -935,89 +1027,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.649999999999999">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:2" ht="27.75">
+      <c r="A2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="41.25">
+      <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="5"/>
-    </row>
-    <row r="2" spans="1:2" ht="27.75">
-      <c r="A2" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="7" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="7" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="41.25">
-      <c r="A4" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="7" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="27.75">
+      <c r="A8" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="7" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="27.75">
+      <c r="A9" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="7" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="27.75">
+      <c r="A10" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="7" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="41.25">
+      <c r="A11" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="27.75">
-      <c r="A8" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="27.75">
-      <c r="A9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="27.75">
-      <c r="A10" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="41.25">
-      <c r="A11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1040,85 +1132,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="11" t="s">
+      <c r="A1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D4" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="12" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="D5" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="12" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="12" t="s">
+      <c r="B6" s="6"/>
+      <c r="C6" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="12" t="s">
+      <c r="D6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D7" s="8" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Mau_nhap_khoa_dao_tao.xlsx
+++ b/Mau_nhap_khoa_dao_tao.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2EE116A-E637-4A86-B4E5-017702270761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A896EC11-7D10-4003-B815-206EE791C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="3" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
   </bookViews>
   <sheets>
     <sheet name="KHOA_DAO_TAO" sheetId="1" r:id="rId1"/>
     <sheet name="HOC_VIEN" sheetId="2" r:id="rId2"/>
-    <sheet name="DANH_MUC" sheetId="3" r:id="rId3"/>
-    <sheet name="HUONG_DAN" sheetId="4" r:id="rId4"/>
+    <sheet name="HUONG_DAN" sheetId="3" r:id="rId3"/>
+    <sheet name="DANH_MUC" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t>Mã tạm khóa (*)</t>
   </si>
@@ -141,12 +141,6 @@
     <t>MẪU NHẬP DỮ LIỆU KHÓA ĐÀO TẠO</t>
   </si>
   <si>
-    <t>Nguyên tắc chung</t>
-  </si>
-  <si>
-    <t>File dùng để chuẩn bị dữ liệu trước khi nhập vào hệ thống. Mã khóa chính thức (ví dụ 2026-HVT-002) không nhập trong Excel; Supabase sẽ tự cấp khi xác nhận nhập.</t>
-  </si>
-  <si>
     <t>Ký hiệu (*)</t>
   </si>
   <si>
@@ -156,51 +150,15 @@
     <t>Mã tạm khóa</t>
   </si>
   <si>
-    <t>Tự đặt trong file, ví dụ K001, K002. Mã này dùng để nối khóa ở sheet KHOA_DAO_TAO với học viên ở sheet HOC_VIEN và không phải mã khóa chính thức.</t>
-  </si>
-  <si>
-    <t>Tên khóa đào tạo</t>
-  </si>
-  <si>
-    <t>Bắt buộc.</t>
-  </si>
-  <si>
     <t>Ngày bắt đầu / kết thúc</t>
   </si>
   <si>
-    <t>Bắt buộc. Ngày kết thúc không được trước ngày bắt đầu.</t>
-  </si>
-  <si>
-    <t>Giờ bắt đầu / kết thúc</t>
-  </si>
-  <si>
-    <t>Có thể để trống. Nếu có, nhập theo dạng HH:MM.</t>
-  </si>
-  <si>
     <t>Tình trạng</t>
   </si>
   <si>
-    <t>Chọn trong danh sách có sẵn: Chưa triển khai, Đang triển khai, Hoàn thành, Tạm hoãn, Hủy.</t>
-  </si>
-  <si>
     <t>Mã nhân sự thực hiện</t>
   </si>
   <si>
-    <t>Bắt buộc. Chọn mã trong danh sách có sẵn; hệ thống dùng mã này để xác định nhân sự phụ trách và sinh mã khóa.</t>
-  </si>
-  <si>
-    <t>HỌC VIÊN</t>
-  </si>
-  <si>
-    <t>Mã tạm khóa và Họ và tên là bắt buộc. Chức danh và Ban/Đơn vị nên có nhưng có thể để trống. Email, SĐT và Nơi công tác là tùy chọn.</t>
-  </si>
-  <si>
-    <t>Lưu ý dữ liệu</t>
-  </si>
-  <si>
-    <t>Không đưa file dữ liệu học viên thực tế lên GitHub public. File mẫu có thể đặt trên website; file đã điền được chọn từ máy tính để website kiểm tra và nhập vào Supabase.</t>
-  </si>
-  <si>
     <t>Mã nhân sự</t>
   </si>
   <si>
@@ -259,6 +217,51 @@
   </si>
   <si>
     <t>05/09/2026; 07/09/2026; 10/09/2026</t>
+  </si>
+  <si>
+    <t>Chuẩn ngày tháng</t>
+  </si>
+  <si>
+    <t>Toàn bộ ngày người dùng nhập và nhìn thấy trong file Excel sử dụng duy nhất định dạng dd/mm/yyyy. Ví dụ: 05/09/2026 là ngày 05 tháng 09 năm 2026. Không sử dụng mm/dd/yy hoặc năm 2 chữ số.</t>
+  </si>
+  <si>
+    <t>Tự đặt trong file, ví dụ K001, K002; dùng để liên kết khóa với học viên. Không phải mã khóa chính thức.</t>
+  </si>
+  <si>
+    <t>Bắt buộc. Nhập theo dd/mm/yyyy. Dùng cho thông tin tổng quát, sắp xếp và báo cáo.</t>
+  </si>
+  <si>
+    <t>Không bắt buộc. Chỉ nhập khi các ngày học không liền nhau; mỗi ngày ghi theo dd/mm/yyyy và cách nhau bằng dấu chấm phẩy (;). Ví dụ: 05/09/2026; 07/09/2026; 10/09/2026.</t>
+  </si>
+  <si>
+    <t>Khóa học liên tục</t>
+  </si>
+  <si>
+    <t>Để trống Ngày học thực tế. Ví dụ từ 05/09/2026 đến 07/09/2026 được hệ thống tính là 3 ngày đào tạo.</t>
+  </si>
+  <si>
+    <t>Khóa học cách ngày</t>
+  </si>
+  <si>
+    <t>Nhập đầy đủ từng ngày vào Ngày học thực tế. Hệ thống sẽ đếm số ngày theo danh sách này và dùng các ngày đó để kiểm tra trùng lịch.</t>
+  </si>
+  <si>
+    <t>Chọn: Chưa triển khai, Đang triển khai, Hoàn thành, Tạm hoãn hoặc Hủy.</t>
+  </si>
+  <si>
+    <t>Bắt buộc. Hệ thống sẽ kiểm tra lại với danh mục nhân sự đang hoạt động trên Supabase.</t>
+  </si>
+  <si>
+    <t>Học viên</t>
+  </si>
+  <si>
+    <t>Mã tạm khóa và Họ và tên là bắt buộc. Chức danh, Ban/Đơn vị nên có nhưng có thể để trống. Email, SĐT, Nơi công tác là tùy chọn.</t>
+  </si>
+  <si>
+    <t>Mã khóa chính thức</t>
+  </si>
+  <si>
+    <t>Không nhập trong Excel. Supabase tự sinh khi xác nhận nhập, theo dạng YYYY-MÃ NHÂN SỰ-STT.</t>
   </si>
 </sst>
 </file>
@@ -266,7 +269,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -391,21 +394,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -415,8 +409,17 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -740,182 +743,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="9">
         <v>46151</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="9">
         <v>46212</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="12">
+      <c r="B3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="9">
         <v>46151</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="9">
         <v>46304</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="10"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -933,25 +936,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="28.5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1019,104 +1022,201 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8487C2A0-BE80-4225-B30E-3AD52D471EF2}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="76.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.649999999999999">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:2" ht="17.649999999999999" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:2" ht="27.75">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="15"/>
+    </row>
+    <row r="2" spans="1:2" ht="41.25">
+      <c r="A2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="14" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+    <row r="4" spans="1:2" ht="27.75">
+      <c r="A4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="13" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="41.25">
-      <c r="A4" s="3" t="s">
+      <c r="B5" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="41.25">
+      <c r="A6" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="27.75">
+      <c r="A7" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="27.75">
+      <c r="A8" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B9" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="27.75">
+      <c r="A10" s="13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="27.75">
-      <c r="A8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="27.75">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="27.75">
-      <c r="A10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="41.25">
-      <c r="A11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="B10" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="27.75">
+      <c r="A11" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="27.75">
+      <c r="A12" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1132,85 +1232,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="7" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Mau_nhap_khoa_dao_tao.xlsx
+++ b/Mau_nhap_khoa_dao_tao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A896EC11-7D10-4003-B815-206EE791C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E455B4A-63F3-4B98-9557-009240E7B6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="3" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
   </bookViews>
   <sheets>
     <sheet name="KHOA_DAO_TAO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>Mã tạm khóa (*)</t>
   </si>
@@ -262,16 +262,22 @@
   </si>
   <si>
     <t>Không nhập trong Excel. Supabase tự sinh khi xác nhận nhập, theo dạng YYYY-MÃ NHÂN SỰ-STT.</t>
+  </si>
+  <si>
+    <t>05/09/2026</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,26 +316,8 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tiem"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Tiem"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,12 +339,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -388,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -400,18 +382,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -420,6 +390,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -735,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF67E0AC-AADB-4307-AE13-44DC1057F665}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="10" width="24.86328125" customWidth="1"/>
@@ -746,31 +722,31 @@
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>8</v>
       </c>
     </row>
@@ -781,13 +757,13 @@
       <c r="B2" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="9">
-        <v>46151</v>
-      </c>
-      <c r="D2" s="9">
-        <v>46212</v>
-      </c>
-      <c r="E2" s="8"/>
+      <c r="C2" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="11"/>
       <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
@@ -804,20 +780,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="27.75">
       <c r="A3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="9">
-        <v>46151</v>
-      </c>
-      <c r="D3" s="9">
-        <v>46304</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>59</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -837,88 +813,64 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1030,96 +982,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.649999999999999" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="41.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="27.75">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="8" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="41.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="27.75">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="27.75">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="8" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="27.75">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="27.75">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="27.75">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="8" t="s">
         <v>74</v>
       </c>
     </row>

--- a/Mau_nhap_khoa_dao_tao.xlsx
+++ b/Mau_nhap_khoa_dao_tao.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E455B4A-63F3-4B98-9557-009240E7B6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2104C4-7948-424D-8EA9-A504E6AD3807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" activeTab="3" xr2:uid="{6197501B-B95F-46C9-9378-27941EA111D2}"/>
   </bookViews>
   <sheets>
     <sheet name="KHOA_DAO_TAO" sheetId="1" r:id="rId1"/>
     <sheet name="HOC_VIEN" sheetId="2" r:id="rId2"/>
-    <sheet name="HUONG_DAN" sheetId="3" r:id="rId3"/>
-    <sheet name="DANH_MUC" sheetId="4" r:id="rId4"/>
+    <sheet name="DANH_MUC" sheetId="4" r:id="rId3"/>
+    <sheet name="HUONG_DAN" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
   <si>
     <t>Mã tạm khóa (*)</t>
   </si>
@@ -105,15 +105,6 @@
     <t>Ban/Đơn vị</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>SĐT</t>
-  </si>
-  <si>
-    <t>Nơi công tác</t>
-  </si>
-  <si>
     <t>Chuyên viên</t>
   </si>
   <si>
@@ -135,9 +126,6 @@
     <t>Ban C</t>
   </si>
   <si>
-    <t>TP. Hồ Chí Minh</t>
-  </si>
-  <si>
     <t>MẪU NHẬP DỮ LIỆU KHÓA ĐÀO TẠO</t>
   </si>
   <si>
@@ -222,48 +210,24 @@
     <t>Chuẩn ngày tháng</t>
   </si>
   <si>
-    <t>Toàn bộ ngày người dùng nhập và nhìn thấy trong file Excel sử dụng duy nhất định dạng dd/mm/yyyy. Ví dụ: 05/09/2026 là ngày 05 tháng 09 năm 2026. Không sử dụng mm/dd/yy hoặc năm 2 chữ số.</t>
-  </si>
-  <si>
     <t>Tự đặt trong file, ví dụ K001, K002; dùng để liên kết khóa với học viên. Không phải mã khóa chính thức.</t>
   </si>
   <si>
-    <t>Bắt buộc. Nhập theo dd/mm/yyyy. Dùng cho thông tin tổng quát, sắp xếp và báo cáo.</t>
-  </si>
-  <si>
-    <t>Không bắt buộc. Chỉ nhập khi các ngày học không liền nhau; mỗi ngày ghi theo dd/mm/yyyy và cách nhau bằng dấu chấm phẩy (;). Ví dụ: 05/09/2026; 07/09/2026; 10/09/2026.</t>
-  </si>
-  <si>
     <t>Khóa học liên tục</t>
   </si>
   <si>
-    <t>Để trống Ngày học thực tế. Ví dụ từ 05/09/2026 đến 07/09/2026 được hệ thống tính là 3 ngày đào tạo.</t>
-  </si>
-  <si>
     <t>Khóa học cách ngày</t>
   </si>
   <si>
-    <t>Nhập đầy đủ từng ngày vào Ngày học thực tế. Hệ thống sẽ đếm số ngày theo danh sách này và dùng các ngày đó để kiểm tra trùng lịch.</t>
-  </si>
-  <si>
     <t>Chọn: Chưa triển khai, Đang triển khai, Hoàn thành, Tạm hoãn hoặc Hủy.</t>
   </si>
   <si>
-    <t>Bắt buộc. Hệ thống sẽ kiểm tra lại với danh mục nhân sự đang hoạt động trên Supabase.</t>
-  </si>
-  <si>
     <t>Học viên</t>
   </si>
   <si>
-    <t>Mã tạm khóa và Họ và tên là bắt buộc. Chức danh, Ban/Đơn vị nên có nhưng có thể để trống. Email, SĐT, Nơi công tác là tùy chọn.</t>
-  </si>
-  <si>
     <t>Mã khóa chính thức</t>
   </si>
   <si>
-    <t>Không nhập trong Excel. Supabase tự sinh khi xác nhận nhập, theo dạng YYYY-MÃ NHÂN SỰ-STT.</t>
-  </si>
-  <si>
     <t>05/09/2026</t>
   </si>
   <si>
@@ -271,22 +235,44 @@
   </si>
   <si>
     <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>Nhập ngày dưới dạng chữ theo duy nhất định dạng dd/mm/yyyy. Ví dụ: 05/09/2026 là ngày 05 tháng 09 năm 2026. Không dùng mm/dd/yy hoặc năm 2 chữ số.</t>
+  </si>
+  <si>
+    <t>Lưu ý quan trọng</t>
+  </si>
+  <si>
+    <t>Các cột Ngày bắt đầu, Ngày kết thúc và Ngày học thực tế đã được định dạng TEXT để Excel không tự đảo ngày/tháng theo thiết lập vùng của máy.</t>
+  </si>
+  <si>
+    <t>Bắt buộc. Nhập đúng dd/mm/yyyy.</t>
+  </si>
+  <si>
+    <t>Không bắt buộc. Chỉ nhập khi các ngày học không liền nhau; cách nhau bằng dấu chấm phẩy (;). Ví dụ: 05/09/2026; 07/09/2026; 10/09/2026.</t>
+  </si>
+  <si>
+    <t>Để trống Ngày học thực tế. Ví dụ 05/09/2026–07/09/2026 được tính là 3 ngày.</t>
+  </si>
+  <si>
+    <t>Nhập đầy đủ từng ngày học. Hệ thống dùng danh sách này để đếm số ngày và kiểm tra trùng lịch.</t>
+  </si>
+  <si>
+    <t>Bắt buộc. Hệ thống kiểm tra với danh mục nhân sự đang hoạt động.</t>
+  </si>
+  <si>
+    <t>Sheet HOC_VIEN chỉ gồm 4 cột: Mã tạm khóa, Họ và tên, Chức danh, Ban/Đơn vị. Trong đó Mã tạm khóa và Họ và tên là bắt buộc; Chức danh và Ban/Đơn vị có thể để trống.</t>
+  </si>
+  <si>
+    <t>Không nhập trong Excel. Supabase tự sinh khi xác nhận nhập.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -317,7 +303,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,12 +320,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF5EE"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -370,32 +350,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,166 +684,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF67E0AC-AADB-4307-AE13-44DC1057F665}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="10" width="24.86328125" customWidth="1"/>
     <col min="11" max="11" width="20.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="8" t="s">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="8" t="s">
+      <c r="B2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="27.75">
-      <c r="A3" s="8" t="s">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="27.75">
+      <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="B3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -880,92 +861,121 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348EEDE3-12AA-4ACD-916D-019EA35B8308}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="28.5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" ht="27.75">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="27.75">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="27.75">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>29</v>
+      <c r="B3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="27.75">
+      <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
+      <c r="B4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -973,206 +983,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8487C2A0-BE80-4225-B30E-3AD52D471EF2}">
-  <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="76.3984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="17.649999999999999" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:2" ht="41.25">
-      <c r="A2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="27.75">
-      <c r="A4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="41.25">
-      <c r="A6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="27.75">
-      <c r="A7" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="27.75">
-      <c r="A8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="27.75">
-      <c r="A10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="27.75">
-      <c r="A11" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="27.75">
-      <c r="A12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FEC9F1A-A1DD-413F-9A50-AAA04E211FB7}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1184,88 +994,559 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="5" t="s">
+      <c r="D2" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="6" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8487C2A0-BE80-4225-B30E-3AD52D471EF2}">
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="76.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="17.649999999999999" customHeight="1">
+      <c r="A1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" ht="27.75">
+      <c r="A2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="27.75">
+      <c r="A3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" ht="27.75">
+      <c r="A5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="27.75">
+      <c r="A7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="27.75">
+      <c r="A9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="41.25">
+      <c r="A12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>